--- a/docs/05-Power-Budget/RAS304.xlsx
+++ b/docs/05-Power-Budget/RAS304.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>Item Name</t>
   </si>
@@ -100,6 +100,27 @@
     </r>
   </si>
   <si>
+    <t>LED Set</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>California JOS 50 PCS Colorful 5mm LED Light Diodes, LED Circuit Assorted Kit for Science Project Experiment (10pieces/Color): Amazon.com: Industrial &amp; Scientific</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>California JOS 50 PCS Colorful 5mm LED Light Diodes, LED Circuit Assorted Kit for Science Project Experiment (10pieces/Color): Amazon.com: Industrial &amp; Scientific</t>
+    </r>
+  </si>
+  <si>
     <t>Resistor Set</t>
   </si>
   <si>
@@ -169,10 +190,19 @@
     <t>3 mA</t>
   </si>
   <si>
+    <t>LEDs</t>
+  </si>
+  <si>
+    <t>10mA each</t>
+  </si>
+  <si>
+    <t>40mA</t>
+  </si>
+  <si>
     <t>TOTAL =</t>
   </si>
   <si>
-    <t>35 mA</t>
+    <t>75mA</t>
   </si>
 </sst>
 </file>
@@ -340,7 +370,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G5" displayName="Bill_of_Materials" name="Bill_of_Materials" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G6" displayName="Bill_of_Materials" name="Bill_of_Materials" id="1">
   <tableColumns count="7">
     <tableColumn name="Item Name" id="1"/>
     <tableColumn name="Qty" id="2"/>
@@ -355,7 +385,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A9:E14" displayName="Power_Budget" name="Power_Budget" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A10:E16" displayName="Power_Budget" name="Power_Budget" id="2">
   <tableColumns count="5">
     <tableColumn name="Component Name" id="1"/>
     <tableColumn name="Qty" id="2"/>
@@ -674,10 +704,10 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="3">
-        <v>9.99</v>
+        <v>4.59</v>
       </c>
       <c r="D5" s="3">
-        <v>9.99</v>
+        <v>4.59</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
@@ -689,56 +719,62 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>9.99</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.99</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2">
         <v>1.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>31</v>
@@ -752,49 +788,83 @@
         <v>33</v>
       </c>
       <c r="B12" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2">
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2">
         <v>3.0</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C2:D5">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C2:D6">
       <formula1>AND(ISNUMBER(C2),(NOT(OR(NOT(ISERROR(DATEVALUE(C2))), AND(ISNUMBER(C2), LEFT(CELL("format", C2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -807,11 +877,13 @@
     <hyperlink r:id="rId6" ref="G4"/>
     <hyperlink r:id="rId7" ref="F5"/>
     <hyperlink r:id="rId8" ref="G5"/>
+    <hyperlink r:id="rId9" ref="F6"/>
+    <hyperlink r:id="rId10" ref="G6"/>
   </hyperlinks>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId11"/>
   <tableParts count="2">
-    <tablePart r:id="rId12"/>
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>